--- a/harga_sembako_desktop.xlsx
+++ b/harga_sembako_desktop.xlsx
@@ -141,7 +141,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
